--- a/game-stats/Week3_PAK-LIONS_vs_LOB.xlsx
+++ b/game-stats/Week3_PAK-LIONS_vs_LOB.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -539,7 +539,7 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
@@ -617,15 +617,20 @@
       </c>
       <c r="O1" s="2" t="inlineStr">
         <is>
+          <t>Def TDs</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -687,6 +692,9 @@
       <c r="Q2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -742,6 +750,9 @@
         <v>0</v>
       </c>
       <c r="Q3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -801,6 +812,9 @@
       <c r="Q4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -858,6 +872,9 @@
       <c r="Q5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -915,6 +932,9 @@
       <c r="Q6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -972,6 +992,9 @@
       <c r="Q7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1029,6 +1052,9 @@
       <c r="Q8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1086,6 +1112,9 @@
       <c r="Q9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1143,6 +1172,9 @@
       <c r="Q10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1200,6 +1232,9 @@
       <c r="Q11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1257,6 +1292,9 @@
       <c r="Q12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1314,6 +1352,9 @@
       <c r="Q13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1371,6 +1412,9 @@
       <c r="Q14" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R14" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1428,6 +1472,9 @@
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1485,6 +1532,9 @@
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1542,6 +1592,9 @@
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1599,6 +1652,9 @@
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1656,6 +1712,9 @@
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R19" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1713,6 +1772,9 @@
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R20" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1770,6 +1832,9 @@
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R21" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1825,6 +1890,9 @@
         <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1839,7 +1907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1856,7 +1924,7 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
@@ -1934,15 +2002,20 @@
       </c>
       <c r="O1" s="2" t="inlineStr">
         <is>
+          <t>Def TDs</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -2004,6 +2077,9 @@
       <c r="Q2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -2061,6 +2137,9 @@
       <c r="Q3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -2118,6 +2197,9 @@
       <c r="Q4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -2175,6 +2257,9 @@
       <c r="Q5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -2232,6 +2317,9 @@
       <c r="Q6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -2289,6 +2377,9 @@
       <c r="Q7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2346,6 +2437,9 @@
       <c r="Q8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -2403,6 +2497,9 @@
       <c r="Q9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -2460,6 +2557,9 @@
       <c r="Q10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -2517,6 +2617,9 @@
       <c r="Q11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -2574,6 +2677,9 @@
       <c r="Q12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -2631,6 +2737,9 @@
       <c r="Q13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -2688,6 +2797,9 @@
       <c r="Q14" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R14" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -2745,6 +2857,9 @@
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -2802,6 +2917,9 @@
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -2859,6 +2977,9 @@
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -2914,6 +3035,9 @@
         <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2973,6 +3097,9 @@
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R19" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -3030,6 +3157,9 @@
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R20" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -3085,6 +3215,9 @@
         <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/game-stats/Week3_PAK-LIONS_vs_LOB.xlsx
+++ b/game-stats/Week3_PAK-LIONS_vs_LOB.xlsx
@@ -5199,7 +5199,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>No Name</t>
+          <t>Charles II</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
